--- a/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,19 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
-  </si>
-  <si>
-    <t>مكرونة بساطة شعرية - 350 جم</t>
+    <t>أولويز ماكسى  سميكة ناعمة بلمسة الألوڤيرا طويلة - 8 فوطة</t>
+  </si>
+  <si>
+    <t>فيبا سائل أطباق تفاح- 4 كجم</t>
+  </si>
+  <si>
+    <t>مناديل فاميليا جيب 2 طبقة - 10 منديل</t>
+  </si>
+  <si>
+    <t>سائل اطباق وفير بلس ليمون اصفر - 40 جم</t>
+  </si>
+  <si>
+    <t>اندومى سوبر مى خضار - 5 جنيه - 56 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,53 +438,104 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>2424</v>
+        <v>4372</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>863.75</v>
+        <v>27.25</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>2424</v>
+        <v>4372</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>172.75</v>
+        <v>436</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>7704</v>
+        <v>5517</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>171.75</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>11089</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>175.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>11677</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>65</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24257</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>209</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,19 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>أولويز ماكسى  سميكة ناعمة بلمسة الألوڤيرا طويلة - 8 فوطة</t>
-  </si>
-  <si>
-    <t>فيبا سائل أطباق تفاح- 4 كجم</t>
-  </si>
-  <si>
-    <t>مناديل فاميليا جيب 2 طبقة - 10 منديل</t>
-  </si>
-  <si>
-    <t>سائل اطباق وفير بلس ليمون اصفر - 40 جم</t>
-  </si>
-  <si>
-    <t>اندومى سوبر مى خضار - 5 جنيه - 56 جم</t>
+    <t>ارز حبوبة رفيع - 1 كجم</t>
+  </si>
+  <si>
+    <t>لبن المراعى كامل دسم بلاستيك - 1 لتر</t>
+  </si>
+  <si>
+    <t>فانتا برتقال -- 1.45 لتر</t>
+  </si>
+  <si>
+    <t>صلصة هاينز - 360 جم</t>
+  </si>
+  <si>
+    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
+  </si>
+  <si>
+    <t>صابون كامى رومانسية - 110 جم</t>
+  </si>
+  <si>
+    <t>بريكس مزيل بقع - 30 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -410,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -438,104 +444,138 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>4372</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>27.25</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>4372</v>
+        <v>990</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>436</v>
+        <v>558</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>5517</v>
+        <v>2774</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>360</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>11089</v>
+        <v>3478</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>175.25</v>
+        <v>382.5</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>11677</v>
+        <v>3934</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>51.25</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24257</v>
+        <v>8286</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>209</v>
+        <v>717</v>
       </c>
       <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>8286</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>59.75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>12503</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>139</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ارز حبوبة رفيع - 1 كجم</t>
-  </si>
-  <si>
-    <t>لبن المراعى كامل دسم بلاستيك - 1 لتر</t>
-  </si>
-  <si>
-    <t>فانتا برتقال -- 1.45 لتر</t>
-  </si>
-  <si>
-    <t>صلصة هاينز - 360 جم</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل فل ازرق يدوى - 2.5 كجم</t>
-  </si>
-  <si>
-    <t>صابون كامى رومانسية - 110 جم</t>
-  </si>
-  <si>
-    <t>بريكس مزيل بقع - 30 جم</t>
+    <t>جبنة عبور لاند رومى - 250 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3</v>
+        <v>5646</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -453,129 +435,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>253</v>
+        <v>525.5</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>990</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>558</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>2774</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>185</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>3478</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>382.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>3934</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>51.25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>8286</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>717</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>8286</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>59.75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>12503</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>139</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_1123_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوكا كولا جيب - 240 مل</t>
+    <t>بيبسى كانز جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>سردين دولفين بارد - 125 جم</t>
+  </si>
+  <si>
+    <t>سائل اطباق وفير بلس ليمون اخضر - 4 كجم</t>
+  </si>
+  <si>
+    <t>كل يوم عصير مانجو - 200 مل</t>
+  </si>
+  <si>
+    <t>ماكسى كانز برتقال اورجينال - 300 مل</t>
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -398,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +441,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>615</v>
+        <v>434</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,10 +450,129 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>305.5</v>
+        <v>303.5</v>
       </c>
       <c r="E2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>1409</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
+      </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>1350</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>1409</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>33.75</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>1409</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1687.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>1409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>506.25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>1691</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>322</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>11838</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>113.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23661</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>275.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
